--- a/output/pdf_financials_xlsx/INEO.xlsx
+++ b/output/pdf_financials_xlsx/INEO.xlsx
@@ -1144,19 +1144,19 @@
         <v>-0.007808</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>4.2e-05</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-0.450776</v>
@@ -1396,19 +1396,19 @@
         <v>-0.007808</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>4.2e-05</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-0.450776</v>
@@ -1543,19 +1543,19 @@
         <v>-0.007808</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4.2e-05</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-0.450776</v>
@@ -1694,10 +1694,10 @@
         <v>-0.251871</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4.2218</v>
+        <v>-4.2218</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7.609292</v>
+        <v>-7.609292</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.553525</v>
+        <v>-2.553525</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>22.5388</v>
@@ -1749,19 +1749,19 @@
         <v>-0.007808</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>4.2e-05</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.450776</v>
@@ -1847,19 +1847,19 @@
         <v>-0.007808</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>4.2e-05</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.450776</v>
@@ -1959,19 +1959,19 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -5023,40 +5023,40 @@
         <v>0.05535</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.101409</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.07015</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.505918</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.727115</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.945182</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.164072</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.339258</v>
       </c>
     </row>
     <row r="93">
@@ -9800,7 +9800,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12182,7 +12186,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13524,7 +13532,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -14724,7 +14736,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -15238,7 +15254,11 @@
           <t>Share-based payment reserves 7</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -16180,7 +16200,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -16774,7 +16798,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -17380,7 +17408,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>0.03465</v>
       </c>
@@ -43334,13 +43366,13 @@
         </is>
       </c>
       <c r="I424" s="5" t="n">
-        <v>0.025018</v>
+        <v>-0.025018</v>
       </c>
       <c r="J424" s="5" t="n">
-        <v>0.102141</v>
+        <v>-0.102141</v>
       </c>
       <c r="K424" s="5" t="n">
-        <v>0.450776</v>
+        <v>-0.450776</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -44435,10 +44467,10 @@
         </is>
       </c>
       <c r="F437" s="5" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="G437" s="5" t="n">
-        <v>0.182623</v>
+        <v>-0.182623</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
@@ -44944,10 +44976,10 @@
         </is>
       </c>
       <c r="E443" s="5" t="n">
-        <v>0.06453100000000001</v>
+        <v>-0.06453100000000001</v>
       </c>
       <c r="F443" s="5" t="n">
-        <v>0.06332699999999999</v>
+        <v>-0.06332699999999999</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/INEO.xlsx
+++ b/output/pdf_financials_xlsx/INEO.xlsx
@@ -2075,46 +2075,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.031876</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.367018</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.204902</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00161</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.649102</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.332697</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.072836</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.252638</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.199328</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.706048</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.36251</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.110909</v>
       </c>
     </row>
     <row r="35">
@@ -2173,46 +2173,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.031876</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.367018</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.204902</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00161</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.649102</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.332697</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.072836</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.252638</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.199328</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.706048</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.36251</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.110909</v>
       </c>
     </row>
     <row r="37">
@@ -2761,46 +2761,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.061503</v>
+        <v>0.029627</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.384518</v>
+        <v>0.0175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.209135</v>
+        <v>0.004233</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01661</v>
+        <v>0.015</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.649102</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.332697</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.182692</v>
+        <v>0.109856</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.27179</v>
+        <v>0.019152</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.272205</v>
+        <v>0.072877</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.977273</v>
+        <v>0.271225</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.484283</v>
+        <v>0.121773</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.007534</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.325057</v>
+        <v>0.214148</v>
       </c>
     </row>
     <row r="49">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -37696,7 +37696,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">

--- a/output/pdf_financials_xlsx/INEO.xlsx
+++ b/output/pdf_financials_xlsx/INEO.xlsx
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.394529</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>1.008173</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.921123</v>
       </c>
     </row>
     <row r="65">
@@ -3768,19 +3768,19 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.008324</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.142551</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.228279</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.253132</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0.6745370000000001</v>
@@ -3835,10 +3835,10 @@
         <v>0.6745370000000001</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1.702323</v>
+        <v>2.710496</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>1.800012</v>
+        <v>2.721135</v>
       </c>
     </row>
     <row r="69">
@@ -4178,10 +4178,10 @@
         <v>0.171655</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.210106</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.166688</v>
+        <v>0.245565</v>
       </c>
     </row>
     <row r="76">
@@ -5455,16 +5455,16 @@
         <v>-0.017036</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>-0.05169</v>
+        <v>-0.053062</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.117285</v>
+        <v>-0.130597</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.110286</v>
+        <v>0.1041</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>-0.105247</v>
+        <v>-0.101715</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>-0.045177</v>
@@ -5709,13 +5709,13 @@
         <v>-0.281898</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.050851</v>
+        <v>-0.064163</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.218068</v>
+        <v>0.211882</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.212863</v>
+        <v>-0.209331</v>
       </c>
       <c r="M106" s="3" t="n">
         <v>0.197218</v>
@@ -5961,25 +5961,25 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003886</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.103249</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.414803</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.346049</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.917977</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.403836</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.771392</v>
       </c>
     </row>
     <row r="112">
@@ -7174,25 +7174,25 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003886</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.103249</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.414803</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.346049</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.917977</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.403836</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.771392</v>
       </c>
     </row>
     <row r="135">
@@ -7231,25 +7231,25 @@
         <v>-0.5257270000000001</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.212429</v>
+        <v>-0.216315</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.028103</v>
+        <v>-1.131352</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.619272</v>
+        <v>-2.034075</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-3.078217</v>
+        <v>-3.424266</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.631447</v>
+        <v>-3.549424</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.859278</v>
+        <v>-1.263114</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-2.865154</v>
+        <v>-3.636546</v>
       </c>
     </row>
   </sheetData>
@@ -19250,7 +19250,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -20798,7 +20802,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -23088,7 +23096,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
